--- a/光伏配储项目/电价数据/2026/黎贝站.xlsx
+++ b/光伏配储项目/电价数据/2026/黎贝站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5738099999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80762</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64463</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5903400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.56635</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45878</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11539</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12682</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06415000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16326</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.5994700000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.91773</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14679</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21787</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.53842</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.14799</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.55089</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64775</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7322799999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.98382</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43184</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65888</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.7108099999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.04689</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.20301</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.8821100000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.10156</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.12838</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.34069</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.53025</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58357</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.42613</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.13517</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86807</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7575299999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5196499999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42549</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70947</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76236</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86997</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9144099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5153</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48557</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8878200000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7269600000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.82177</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7709400000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.98597</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.90242</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8553099999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.4982200000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70949</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.12236</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08076</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.04882</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54218</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49419</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8798899999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6360800000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7889400000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8371499999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18913</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.53859</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19566</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87775</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23444</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.13603</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.29078</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.07082</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.12119</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.01398</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03634</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.99066</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.0029</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.82245</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78679</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80463</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33463</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48665</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.49025</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23489</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.54584</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82608</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.58482</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72597</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81349</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.51376</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81174</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.86241</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.66591</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60148</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.55648</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56969</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5942200000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54164</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5615599999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27075</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61727</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45601</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50887</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54049</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6553300000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6317699999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5686599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.5153099999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44454</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61151</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.67238</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56313</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.81279</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6634800000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55924</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48101</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61495</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.46209</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45712</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34199</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52662</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49228</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43541</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.18185</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.59358</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.49287</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.43265</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60336</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48145</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.65543</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.57352</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49585</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46243</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47484</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51951</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.63091</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5134299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49157</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49919</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31946</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.49935</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20423</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.20954</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.15352</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.03579</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22055</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.14508</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21748</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05988</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.03012</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.01627</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.78006</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46198</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48774</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34494</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5966699999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27916</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10267</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04351</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05821</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.22262</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06192</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07831999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07658</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33191</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31451</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78526</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8653</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33088</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39992</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20702</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5622699999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87719</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46732</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55568</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82459</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5769299999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85612</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63678</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.64964</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59849</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.11769</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34812</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91401</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44673</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18681</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44232</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5422100000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87188</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45767</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14531</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69011</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7805700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64137</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49274</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48824</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52896</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24886</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15905</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00043</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5467000000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7932899999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31002</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24488</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13562</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10206</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.09662999999999999</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13142</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.11774</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.23813</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10222</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24155</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.11356</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.23312</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.10845</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.07518999999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.08253000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11135</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18106</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.12373</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33646</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49752</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23866</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4667</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.26242</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.30243</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.25872</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67149</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.52423</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.19462</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5804600000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.6253500000000001</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.90774</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.43279</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5167200000000001</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.53651</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7076699999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7064900000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.67398</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50481</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31907</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.63063</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34431</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.59527</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65159</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7871699999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.44455</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33608</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21992</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.23354</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63997</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59805</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6021299999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.71729</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48549</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35154</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53638</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48141</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.62942</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.39945</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42569</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50743</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.52255</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.56969</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.60619</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6201599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6858099999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67543</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.53701</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.99748</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.40116</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46319</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47667</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47734</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.63274</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.74487</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.82713</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.72593</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.64923</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5407799999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.74722</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76575</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6185700000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6671699999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4884</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45315</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44232</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51239</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.25947</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.93329</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.47471</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.14752</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33764</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.26069</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19217</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10119</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03562</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19092</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.22049</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24715</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3282</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.25113</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.25346</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.25042</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.25106</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25628</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17103</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21887</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01352</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14587</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02044</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01523</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04059</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04821</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02911</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03885</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01866</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03624</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20084</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25381</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32942</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.73682</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8489800000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8729600000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83904</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21278</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25761</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00066</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26259</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46927</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.52484</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79914</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7717200000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7822899999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.35841</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9835700000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7731699999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.84109</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.8038500000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84068</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83885</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84323</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94032</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7651</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.79976</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.76777</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36562</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61893</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6782899999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5799800000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.49533</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46816</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.42396</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.37713</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.4596</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.3683</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.41604</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.40016</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.76676</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47164</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.42713</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43197</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.58037</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.78128</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.56496</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52628</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.57974</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.46393</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.48193</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47825</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.70299</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83628</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.80675</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46728</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.54343</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5658300000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.8149299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.85997</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7393999999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.58172</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.44633</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23977</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35717</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46105</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5269199999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.61529</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.96814</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8437100000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.74652</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.80569</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5174099999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.63037</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63955</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48839</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8400700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.79918</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.02176</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.90049</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.83082</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7982400000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46466</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36154</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.26684</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.33605</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25628</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.51258</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.18241</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.59248</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45195</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5420900000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45214</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.44725</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36803</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9894500000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.44771</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.59987</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.51835</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1.36869</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1.46386</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.5238200000000001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50929</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51081</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36121</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17474</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14445</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19674</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12529</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16243</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14503</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20837</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26117</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19586</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14279</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48741</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.38091</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47355</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38612</v>
       </c>
     </row>
   </sheetData>
